--- a/Drawings/Velocity_SE-RG_Part_Register.xlsx
+++ b/Drawings/Velocity_SE-RG_Part_Register.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\paubur\Documents\GitHub\velocity\Drawings\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C81C16F8-D4F6-456C-A559-DA90E41901CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43AF05BC-C3A4-4C94-B334-1A5191C9F00E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -378,10 +378,10 @@
     <t>Firewall Aft Engine</t>
   </si>
   <si>
-    <t>Pyramid for painting - 3D pritned</t>
+    <t>Paint</t>
   </si>
   <si>
-    <t>Paint</t>
+    <t>Pyramid for painting - 3D printed</t>
   </si>
 </sst>
 </file>
@@ -581,6 +581,9 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -588,9 +591,6 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -905,65 +905,65 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="24"/>
-      <c r="E1" s="24"/>
-      <c r="F1" s="24"/>
-      <c r="G1" s="24"/>
-      <c r="H1" s="24"/>
-      <c r="I1" s="24"/>
-      <c r="J1" s="24"/>
-      <c r="K1" s="24"/>
-      <c r="L1" s="24"/>
-      <c r="M1" s="24"/>
-      <c r="N1" s="24"/>
-      <c r="O1" s="24"/>
-      <c r="P1" s="24"/>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="25"/>
+      <c r="H1" s="25"/>
+      <c r="I1" s="25"/>
+      <c r="J1" s="25"/>
+      <c r="K1" s="25"/>
+      <c r="L1" s="25"/>
+      <c r="M1" s="25"/>
+      <c r="N1" s="25"/>
+      <c r="O1" s="25"/>
+      <c r="P1" s="25"/>
     </row>
     <row r="2" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="25" t="s">
+      <c r="A2" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="25"/>
-      <c r="C2" s="25"/>
-      <c r="D2" s="25"/>
-      <c r="E2" s="25"/>
-      <c r="F2" s="25"/>
-      <c r="G2" s="25"/>
-      <c r="H2" s="25"/>
-      <c r="I2" s="25"/>
-      <c r="J2" s="25"/>
-      <c r="K2" s="25"/>
-      <c r="L2" s="25"/>
-      <c r="M2" s="25"/>
-      <c r="N2" s="25"/>
-      <c r="O2" s="25"/>
-      <c r="P2" s="25"/>
+      <c r="B2" s="26"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="26"/>
+      <c r="F2" s="26"/>
+      <c r="G2" s="26"/>
+      <c r="H2" s="26"/>
+      <c r="I2" s="26"/>
+      <c r="J2" s="26"/>
+      <c r="K2" s="26"/>
+      <c r="L2" s="26"/>
+      <c r="M2" s="26"/>
+      <c r="N2" s="26"/>
+      <c r="O2" s="26"/>
+      <c r="P2" s="26"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A3" s="26" t="str">
+      <c r="A3" s="27" t="str">
         <f>IF(SUMPRODUCT((C5:C504&lt;&gt;"")/COUNTIF(C5:C504,C5:C504&amp;""))&lt;COUNTA(C5:C504),"⚠ DUPLICATE PAYLOAD IN USE — see red cells below","")</f>
         <v/>
       </c>
-      <c r="B3" s="26"/>
-      <c r="C3" s="26"/>
-      <c r="D3" s="26"/>
-      <c r="E3" s="26"/>
-      <c r="F3" s="26"/>
-      <c r="G3" s="26"/>
-      <c r="H3" s="26"/>
-      <c r="I3" s="26"/>
-      <c r="J3" s="26"/>
-      <c r="K3" s="26"/>
-      <c r="L3" s="26"/>
-      <c r="M3" s="26"/>
-      <c r="N3" s="26"/>
-      <c r="O3" s="26"/>
-      <c r="P3" s="26"/>
+      <c r="B3" s="27"/>
+      <c r="C3" s="27"/>
+      <c r="D3" s="27"/>
+      <c r="E3" s="27"/>
+      <c r="F3" s="27"/>
+      <c r="G3" s="27"/>
+      <c r="H3" s="27"/>
+      <c r="I3" s="27"/>
+      <c r="J3" s="27"/>
+      <c r="K3" s="27"/>
+      <c r="L3" s="27"/>
+      <c r="M3" s="27"/>
+      <c r="N3" s="27"/>
+      <c r="O3" s="27"/>
+      <c r="P3" s="27"/>
     </row>
     <row r="4" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
@@ -1081,18 +1081,18 @@
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
-      <c r="E6" s="30" t="s">
+      <c r="E6" s="24" t="s">
         <v>19</v>
       </c>
       <c r="F6" s="22" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G6" s="4" t="str">
         <f>IFERROR(VLOOKUP(B6,Reference!$A$5:$B$17,2,FALSE()),"")</f>
         <v>Workshop</v>
       </c>
       <c r="H6" s="22" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="I6" s="7" t="s">
         <v>106</v>
@@ -14620,20 +14620,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="24"/>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
     </row>
     <row r="2" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="25" t="s">
+      <c r="A2" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="B2" s="25"/>
-      <c r="C2" s="25"/>
-      <c r="D2" s="25"/>
+      <c r="B2" s="26"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="26"/>
     </row>
     <row r="4" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -14649,12 +14649,12 @@
       </c>
     </row>
     <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="28" t="s">
+      <c r="A6" s="29" t="s">
         <v>23</v>
       </c>
-      <c r="B6" s="28"/>
-      <c r="C6" s="28"/>
-      <c r="D6" s="28"/>
+      <c r="B6" s="29"/>
+      <c r="C6" s="29"/>
+      <c r="D6" s="29"/>
     </row>
     <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
@@ -14692,44 +14692,44 @@
       </c>
     </row>
     <row r="12" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="27" t="s">
+      <c r="A12" s="28" t="s">
         <v>26</v>
       </c>
-      <c r="B12" s="27"/>
-      <c r="C12" s="27"/>
-      <c r="D12" s="27"/>
+      <c r="B12" s="28"/>
+      <c r="C12" s="28"/>
+      <c r="D12" s="28"/>
     </row>
     <row r="13" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="27" t="s">
+      <c r="A13" s="28" t="s">
         <v>27</v>
       </c>
-      <c r="B13" s="27"/>
-      <c r="C13" s="27"/>
-      <c r="D13" s="27"/>
+      <c r="B13" s="28"/>
+      <c r="C13" s="28"/>
+      <c r="D13" s="28"/>
     </row>
     <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="27" t="s">
+      <c r="A14" s="28" t="s">
         <v>28</v>
       </c>
-      <c r="B14" s="27"/>
-      <c r="C14" s="27"/>
-      <c r="D14" s="27"/>
+      <c r="B14" s="28"/>
+      <c r="C14" s="28"/>
+      <c r="D14" s="28"/>
     </row>
     <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="27" t="s">
+      <c r="A15" s="28" t="s">
         <v>29</v>
       </c>
-      <c r="B15" s="27"/>
-      <c r="C15" s="27"/>
-      <c r="D15" s="27"/>
+      <c r="B15" s="28"/>
+      <c r="C15" s="28"/>
+      <c r="D15" s="28"/>
     </row>
     <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="27" t="s">
+      <c r="A16" s="28" t="s">
         <v>30</v>
       </c>
-      <c r="B16" s="27"/>
-      <c r="C16" s="27"/>
-      <c r="D16" s="27"/>
+      <c r="B16" s="28"/>
+      <c r="C16" s="28"/>
+      <c r="D16" s="28"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -14757,20 +14757,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="25" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
     </row>
     <row r="2" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="25" t="s">
+      <c r="A2" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="B2" s="25"/>
-      <c r="C2" s="25"/>
-      <c r="D2" s="25"/>
-      <c r="E2" s="25"/>
+      <c r="B2" s="26"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="26"/>
     </row>
     <row r="4" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -14827,11 +14827,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
     </row>
     <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="14" t="s">
@@ -15001,37 +15001,37 @@
       <c r="A21" s="17" t="s">
         <v>77</v>
       </c>
-      <c r="B21" s="29" t="s">
+      <c r="B21" s="30" t="s">
         <v>78</v>
       </c>
-      <c r="C21" s="29"/>
+      <c r="C21" s="30"/>
     </row>
     <row r="22" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="17" t="s">
         <v>79</v>
       </c>
-      <c r="B22" s="29" t="s">
+      <c r="B22" s="30" t="s">
         <v>80</v>
       </c>
-      <c r="C22" s="29"/>
+      <c r="C22" s="30"/>
     </row>
     <row r="23" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="17" t="s">
         <v>81</v>
       </c>
-      <c r="B23" s="29" t="s">
+      <c r="B23" s="30" t="s">
         <v>82</v>
       </c>
-      <c r="C23" s="29"/>
+      <c r="C23" s="30"/>
     </row>
     <row r="24" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="17" t="s">
         <v>83</v>
       </c>
-      <c r="B24" s="29" t="s">
+      <c r="B24" s="30" t="s">
         <v>84</v>
       </c>
-      <c r="C24" s="29"/>
+      <c r="C24" s="30"/>
     </row>
     <row r="27" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="14" t="s">
@@ -15042,69 +15042,69 @@
       <c r="A28" s="17" t="s">
         <v>86</v>
       </c>
-      <c r="B28" s="29" t="s">
+      <c r="B28" s="30" t="s">
         <v>87</v>
       </c>
-      <c r="C28" s="29"/>
+      <c r="C28" s="30"/>
     </row>
     <row r="29" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="17" t="s">
         <v>88</v>
       </c>
-      <c r="B29" s="29" t="s">
+      <c r="B29" s="30" t="s">
         <v>89</v>
       </c>
-      <c r="C29" s="29"/>
+      <c r="C29" s="30"/>
     </row>
     <row r="30" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="17" t="s">
         <v>90</v>
       </c>
-      <c r="B30" s="29" t="s">
+      <c r="B30" s="30" t="s">
         <v>91</v>
       </c>
-      <c r="C30" s="29"/>
+      <c r="C30" s="30"/>
     </row>
     <row r="31" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="17" t="s">
         <v>92</v>
       </c>
-      <c r="B31" s="29" t="s">
+      <c r="B31" s="30" t="s">
         <v>93</v>
       </c>
-      <c r="C31" s="29"/>
+      <c r="C31" s="30"/>
     </row>
     <row r="32" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="17" t="s">
         <v>94</v>
       </c>
-      <c r="B32" s="29" t="s">
+      <c r="B32" s="30" t="s">
         <v>95</v>
       </c>
-      <c r="C32" s="29"/>
+      <c r="C32" s="30"/>
     </row>
     <row r="33" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="B33" s="29" t="s">
+      <c r="B33" s="30" t="s">
         <v>97</v>
       </c>
-      <c r="C33" s="29"/>
+      <c r="C33" s="30"/>
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B24:C24"/>
     <mergeCell ref="B33:C33"/>
     <mergeCell ref="B28:C28"/>
     <mergeCell ref="B29:C29"/>
     <mergeCell ref="B30:C30"/>
     <mergeCell ref="B31:C31"/>
     <mergeCell ref="B32:C32"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B24:C24"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -15123,20 +15123,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="25" t="s">
         <v>98</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="24"/>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="25" t="s">
+      <c r="A2" s="26" t="s">
         <v>99</v>
       </c>
-      <c r="B2" s="25"/>
-      <c r="C2" s="25"/>
-      <c r="D2" s="25"/>
+      <c r="B2" s="26"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="26"/>
     </row>
     <row r="4" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
@@ -15378,12 +15378,12 @@
       <c r="A20" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="B20" s="27" t="str">
+      <c r="B20" s="28" t="str">
         <f>IFERROR("payloads used: "&amp;COUNTA(Register!C5:C504)&amp;" of 9000  |  next: "&amp;(MAX(Register!C5:C504)+1)&amp;"  |  highest: "&amp;MAX(Register!C5:C504),"none yet")</f>
         <v>payloads used: 2 of 9000  |  next: 1002  |  highest: 1001</v>
       </c>
-      <c r="C20" s="27"/>
-      <c r="D20" s="27"/>
+      <c r="C20" s="28"/>
+      <c r="D20" s="28"/>
     </row>
   </sheetData>
   <mergeCells count="3">
